--- a/src/data/COREP_files/G_EU_C_C0902.xlsx
+++ b/src/data/COREP_files/G_EU_C_C0902.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -597,6 +597,15 @@
           <t>Central governments or central banks</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>71</v>
+      </c>
+      <c r="L8" t="n">
+        <v>72</v>
+      </c>
+      <c r="N8" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -609,6 +618,15 @@
           <t>Institutions</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>72</v>
+      </c>
+      <c r="L9" t="n">
+        <v>73</v>
+      </c>
+      <c r="N9" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -621,6 +639,15 @@
           <t>Corporates</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>73</v>
+      </c>
+      <c r="L10" t="n">
+        <v>74</v>
+      </c>
+      <c r="N10" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -645,6 +672,15 @@
           <t>Of Which: SME</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>76</v>
+      </c>
+      <c r="N12" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -657,6 +693,15 @@
           <t>Retail</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>76</v>
+      </c>
+      <c r="L13" t="n">
+        <v>77</v>
+      </c>
+      <c r="N13" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -669,6 +714,15 @@
           <t>Secured by real estate property</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>78</v>
+      </c>
+      <c r="N14" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -681,6 +735,15 @@
           <t>SME</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>78</v>
+      </c>
+      <c r="L15" t="n">
+        <v>79</v>
+      </c>
+      <c r="N15" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -693,6 +756,15 @@
           <t>Non-SME</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>79</v>
+      </c>
+      <c r="L16" t="n">
+        <v>80</v>
+      </c>
+      <c r="N16" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -705,6 +777,15 @@
           <t>Qualifying Revolving</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>71</v>
+      </c>
+      <c r="L17" t="n">
+        <v>72</v>
+      </c>
+      <c r="N17" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -717,6 +798,15 @@
           <t>Other Retail</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>72</v>
+      </c>
+      <c r="L18" t="n">
+        <v>73</v>
+      </c>
+      <c r="N18" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -729,6 +819,15 @@
           <t>SME</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>73</v>
+      </c>
+      <c r="L19" t="n">
+        <v>74</v>
+      </c>
+      <c r="N19" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -741,6 +840,15 @@
           <t>Non-SME</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>74</v>
+      </c>
+      <c r="L20" t="n">
+        <v>75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -753,6 +861,15 @@
           <t>Equity</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>75</v>
+      </c>
+      <c r="L21" t="n">
+        <v>76</v>
+      </c>
+      <c r="N21" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="22">
       <c r="C22" t="inlineStr">
@@ -761,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
